--- a/perfume_catalog.xlsx
+++ b/perfume_catalog.xlsx
@@ -3283,7 +3283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.142857142857141" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3292,7 +3292,7 @@
           <t>Brands</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>why</t>
         </is>
@@ -3383,492 +3383,456 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>Clive Dorris Collection</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>first-copy house</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fragrance Deluxe</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>Perfume Box</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>first-copy house</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Perfume Box</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>first-copy house</t>
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>Generic Xim</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Generic Xim</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>Mini</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Mini</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>Beauty</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Beauty</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>Fragrance</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Fragrance</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>EDP</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>women's</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>women's</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>Men'S</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Men'S</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>VIP MEN</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>VIP MEN</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>Versachem</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Versachem</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>Versse</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Versse</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>Le Versant</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Le Versant</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>Lancom</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Lancom</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t>Giorgi</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Giorgi</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t>Dio</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Dio</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>Hermia</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Hermia</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>Dolcir</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Dolcir</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>Emporio</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Emporio</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t>Yves</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Yves</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t>Yves St-Laurent</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Yves St-Laurent</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t>Gu</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Gu</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>ZAT</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ZAT</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>Bv</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Bv</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>Dg</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Dg</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t>Ck</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Ck</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>typosquat</t>
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>Sauvage</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Sauvage</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>Black Opium</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Black Opium</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t>Invictus</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Invictus</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t>Idole</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Idole</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t>My Way</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>My Way</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t>Asad</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Asad</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t>Hawas</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Hawas</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Shalimar</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>product-name-as-brand</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>product-name-as-brand</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>product-name-as-brand</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
         <is>
           <t>Spice</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
